--- a/benchmarking_automation/final_outputs/accuracy_report.xlsx
+++ b/benchmarking_automation/final_outputs/accuracy_report.xlsx
@@ -62,14 +62,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-        <bgColor rgb="00D9D9D9"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -120,7 +120,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -607,7 +607,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SKY-2000-101</t>
+          <t>Stendarr, Inc.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -615,13 +615,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.0769</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -720,12 +720,12 @@
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -734,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Medical Investigator                     Stendarr, Inc. IRB Approved Version DD Mon YYYY</t>
+          <t>Stendarr, Inc.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -784,13 +784,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.3415</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -902,21 +902,21 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>SKY-2000-101</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
+          <t>A First-In-Human, Phase 1, Randomized, Double-Blind, Placebo-Controlled Study to Evaluate the Safety, Tolerability, and Pharmacokinetics of ABC-123 as a Single Dose in Healthy Participants and as Multiple Doses in Participants with Grade 2 Boneitis</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.0154</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -1015,12 +1015,12 @@
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -1029,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -1058,12 +1058,12 @@
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="M10" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>SKY-2000-101</t>
+          <t>Stendarr, Inc.</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1185,13 +1185,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.0769</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
@@ -1290,12 +1290,12 @@
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -1304,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="M14" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Medical Investigator                     Stendarr, Inc. IRB Approved Version DD Mon YYYY</t>
+          <t>Stendarr, Inc.</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1354,13 +1354,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.3415</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -1396,12 +1396,12 @@
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -1410,7 +1410,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="M16" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -1452,21 +1452,21 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>The study drug is “investigational”. This means that it has not been approved by the United States Food and Drug Administration (FDA).</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
+          <t>a disease that causes bones to change shape or disappear</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.2632</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
@@ -1515,21 +1515,21 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>This is a first-in-human, Phase 1 study. This means the study drug has never been given to humans before. The list of known risks/discomforts is listed later in this informed consent.</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
+          <t>first-in-human, Phase 1</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.2233</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
@@ -1578,21 +1578,21 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>There will be up to 28 participants total in this study.</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
+          <t>28 participants</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL (&gt;=70%)</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.5455</v>
+        <v>0.8333</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Safety measurements, such as ECG, vital signs, laboratory tests, and physical examinations, will be conducted at specific intervals according to the Schedule of Activities (SoA).</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
+          <t>The study is designed as a double-blind, randomized, placebo-controlled trial to evaluate the safety and pharmacokinetics of ABC-123. It includes a Single Ascending Dose (SAD) phase, which involves healthy volunteers, and a repeat-dose component for participants diagnosed with boneitis. The primary objectives are to assess the investigational drug's safety profile and gather data to support future therapeutic developments.</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.0323</v>
+        <v>0.2249</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
@@ -1727,26 +1727,26 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>KEYVALUE</t>
+          <t>LIST</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>During the repeat-dose phase:</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
+          <t>the single ascending dose (SAD) portion of the study</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL (&gt;=70%)</t>
         </is>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.4516</v>
+        <v>0.7294</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
@@ -1795,21 +1795,21 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Be able to follow the study directions and procedures.</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
+          <t>2 to 4 weeks</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.2121</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
@@ -1889,26 +1889,26 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>KEYVALUE</t>
+          <t>LIST</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Screening</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
+          <t>subcutaneous injection</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.3571</v>
+        <v>0.3415</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
@@ -1944,12 +1944,12 @@
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -1958,7 +1958,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="M24" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -1987,12 +1987,12 @@
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -2043,21 +2043,21 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Be able to follow the study directions and procedures.</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
+          <t>2 to 4 weeks</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.2121</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
@@ -2137,26 +2137,26 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>KEYVALUE</t>
+          <t>LIST</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Screening</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
+          <t>subcutaneous injection</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.3571</v>
+        <v>0.3415</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
@@ -2192,12 +2192,12 @@
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -2206,7 +2206,7 @@
         <v>0</v>
       </c>
       <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="M28" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -2248,21 +2248,21 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Participants must abstain from caffeine- or xanthine-containing products (e.g., coffee, tea, cola drinks, and chocolate) from 24 hours before Check-in until Check-out from the CRU.</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
+          <t>every other week for 3 doses</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL (&gt;=70%)</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.1586</v>
+        <v>0.7467</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
@@ -2290,12 +2290,12 @@
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -2304,7 +2304,7 @@
         <v>0</v>
       </c>
       <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="M30" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>SKY-2000-101</t>
+          <t>Stendarr, Inc.</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -2354,13 +2354,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.0769</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
@@ -2459,12 +2459,12 @@
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -2473,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="4" t="inlineStr">
+      <c r="M33" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Medical Investigator                     Stendarr, Inc. IRB Approved Version DD Mon YYYY</t>
+          <t>Stendarr, Inc.</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -2523,13 +2523,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.3415</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
@@ -2578,21 +2578,21 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>This study drug is intended to treat patients with boneitis (a disease that causes bones to change shape or disappear).</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
+          <t>boneitis</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.126</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>The study drug is “investigational”. This means that it has not been approved by the United States Food and Drug Administration (FDA).</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
+          <t>a disease that causes bones to change shape or disappear</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.2632</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
@@ -2732,21 +2732,21 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Safety measurements, such as ECG, vital signs, laboratory tests, and physical examinations, will be conducted at specific intervals according to the Schedule of Activities (SoA).</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
+          <t>The study is designed as a double-blind, randomized, placebo-controlled trial to evaluate the safety and pharmacokinetics of ABC-123. It includes a Single Ascending Dose (SAD) phase, which involves healthy volunteers, and a repeat-dose component for participants diagnosed with boneitis. The primary objectives are to assess the investigational drug's safety profile and gather data to support future therapeutic developments.</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.0509</v>
+        <v>0.073</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
@@ -2790,26 +2790,26 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>KEYVALUE</t>
+          <t>LIST</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>During the repeat-dose phase:</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
+          <t>the single ascending dose (SAD) portion of the study</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL (&gt;=70%)</t>
         </is>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.4516</v>
+        <v>0.7294</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Up to 6 cohorts (or groups) of 6 participants will be given a subcutaneous administration of ABC-123 or placebo. The first cohort will receive the starting dose, and later cohorts will be given higher and higher dose levels until a safe limit is found. The starting dose will begin at 5 mg. This is 318-fold lower than the highest dose tested in animals.</t>
+          <t>6 cohorts (or groups) of 6 participants</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -2866,13 +2866,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL (&gt;=70%)</t>
         </is>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.1365</v>
+        <v>0.7879</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
@@ -2952,26 +2952,26 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>KEYVALUE</t>
+          <t>LIST</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Screening</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
+          <t>subcutaneous injection</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J40" s="4" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.3571</v>
+        <v>0.3415</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
@@ -3007,12 +3007,12 @@
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -3021,7 +3021,7 @@
         <v>0</v>
       </c>
       <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="4" t="inlineStr">
+      <c r="M41" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -3050,12 +3050,12 @@
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="I42" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J42" s="4" t="inlineStr">
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -3064,7 +3064,7 @@
         <v>0</v>
       </c>
       <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="4" t="inlineStr">
+      <c r="M42" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -3093,12 +3093,12 @@
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I43" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J43" s="4" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -3107,7 +3107,7 @@
         <v>0</v>
       </c>
       <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="4" t="inlineStr">
+      <c r="M43" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -3151,21 +3151,21 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Men and women with known heart disease or clinically significant abnormalities identified in the 12-lead ECG at Screening, ages 18 to 65 years, are expected to be in repeat-dose study of this study. During the repeat-dose portion, the study will last about 15 weeks, including up to 5 weeks for Screening, followed by 3 doses administered every other week, and concluding with a Follow-up period..</t>
-        </is>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
+          <t>Cohort 1 will include 8 participants, with 6 receiving the active drug and 2 receiving a placebo. To ensure safety, 2 sentinel participants will be dosed first, one with the active drug and one with the placebo, followed by the remaining participants after a safety review.</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J44" s="4" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.0571</v>
+        <v>0.2325</v>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Participants will return for their second Check-in, scheduled for Day X, where evaluations and procedures as outlined in the Schedule of Assessments (SoA) will be conducted. This includes follow-up assessments to monitor the effects of the study intervention and ensure participant safety.</t>
+          <t>Day 7</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -3222,13 +3222,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J45" s="4" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.381</v>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
@@ -3264,12 +3264,12 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="I46" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J46" s="4" t="inlineStr">
+      <c r="J46" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="4" t="inlineStr">
+      <c r="M46" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>While participating in this research study, you will need to follow these conditions:</t>
+          <t>6 cohorts of 8 participants</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -3328,13 +3328,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL (&gt;=70%)</t>
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.2342</v>
+        <v>0.9434</v>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
@@ -3414,26 +3414,26 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>KEYVALUE</t>
+          <t>LIST</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Screening</t>
-        </is>
-      </c>
-      <c r="I48" s="4" t="inlineStr">
+          <t>subcutaneous injection</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J48" s="4" t="inlineStr">
+      <c r="J48" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.3571</v>
+        <v>0.3415</v>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
@@ -3469,12 +3469,12 @@
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I49" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J49" s="4" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -3483,7 +3483,7 @@
         <v>0</v>
       </c>
       <c r="L49" s="2" t="inlineStr"/>
-      <c r="M49" s="4" t="inlineStr">
+      <c r="M49" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -3525,21 +3525,21 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Participants must abstain from caffeine- or xanthine-containing products (e.g., coffee, tea, cola drinks, and chocolate) from 24 hours before Check-in until Check-out from the CRU.</t>
-        </is>
-      </c>
-      <c r="I50" s="4" t="inlineStr">
+          <t>every other week for 3 doses</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL (&gt;=70%)</t>
         </is>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.1586</v>
+        <v>0.7467</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Pro00050709.</t>
-        </is>
-      </c>
-      <c r="I51" s="4" t="inlineStr">
+          <t>selection of the dose for the repeat-dose portion of the study was based on safety, tolerability, and PK data obtained during the SAD portion of the study</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>LOW SIMILARITY</t>
         </is>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.048</v>
+        <v>0.6142</v>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Follow-Up Visits</t>
+          <t>18 to 55 years old</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -3660,13 +3660,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL (&gt;=70%)</t>
         </is>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.2</v>
+        <v>0.875</v>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
@@ -3710,26 +3710,26 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>KEYVALUE</t>
+          <t>LIST</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>During the repeat-dose phase:</t>
-        </is>
-      </c>
-      <c r="I53" s="4" t="inlineStr">
+          <t>the single ascending dose (SAD) portion of the study</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL (&gt;=70%)</t>
         </is>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.4516</v>
+        <v>0.7294</v>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
@@ -3773,26 +3773,26 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>KEYVALUE</t>
+          <t>LIST</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>During the repeat-dose phase:</t>
-        </is>
-      </c>
-      <c r="I54" s="4" t="inlineStr">
+          <t>the single ascending dose (SAD) portion of the study</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL (&gt;=70%)</t>
         </is>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.4516</v>
+        <v>0.7294</v>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
@@ -3828,12 +3828,12 @@
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I55" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J55" s="4" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -3842,7 +3842,7 @@
         <v>0</v>
       </c>
       <c r="L55" s="2" t="inlineStr"/>
-      <c r="M55" s="4" t="inlineStr">
+      <c r="M55" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -3883,12 +3883,12 @@
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="5" t="inlineStr">
+      <c r="I56" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J56" s="4" t="inlineStr">
+      <c r="J56" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -3897,7 +3897,7 @@
         <v>0</v>
       </c>
       <c r="L56" s="2" t="inlineStr"/>
-      <c r="M56" s="4" t="inlineStr">
+      <c r="M56" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -3926,12 +3926,12 @@
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="5" t="inlineStr">
+      <c r="I57" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J57" s="4" t="inlineStr">
+      <c r="J57" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -3940,7 +3940,7 @@
         <v>0</v>
       </c>
       <c r="L57" s="2" t="inlineStr"/>
-      <c r="M57" s="4" t="inlineStr">
+      <c r="M57" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -3990,21 +3990,21 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Physical examination and vital sign measurement.</t>
-        </is>
-      </c>
-      <c r="I58" s="4" t="inlineStr">
+          <t>up to 15 weeks (up to 5 weeks for screening, repeat-dose every other week for 3 doses SC, and follow-up period)</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>LOW SIMILARITY</t>
         </is>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.2486</v>
+        <v>0.6613</v>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
@@ -4061,21 +4061,21 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Early Discontinuation</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="inlineStr">
+          <t>known heart disease or clinically significant abnormalities identified in the 12-lead ECG at Screening</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J59" s="4" t="inlineStr">
+      <c r="J59" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.1905</v>
+        <v>0.2439</v>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Follow-Up Visits</t>
+          <t>18 to 55 years old</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -4132,13 +4132,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL (&gt;=70%)</t>
         </is>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.2</v>
+        <v>0.875</v>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
@@ -4174,12 +4174,12 @@
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="I61" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J61" s="4" t="inlineStr">
+      <c r="J61" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -4188,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="L61" s="2" t="inlineStr"/>
-      <c r="M61" s="4" t="inlineStr">
+      <c r="M61" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -4217,12 +4217,12 @@
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="5" t="inlineStr">
+      <c r="I62" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J62" s="4" t="inlineStr">
+      <c r="J62" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="L62" s="2" t="inlineStr"/>
-      <c r="M62" s="4" t="inlineStr">
+      <c r="M62" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -4281,21 +4281,21 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>YOU SHOULD NOT SIGN AND DATE THIS CONSENT FORM.</t>
-        </is>
-      </c>
-      <c r="I63" s="4" t="inlineStr">
+          <t>15 weeks, including up to 5 weeks for Screening, followed by 3 doses administered every other week, and concluding with a Follow-up period.</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL (&gt;=70%)</t>
         </is>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.2484</v>
+        <v>0.751</v>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Vaccinations must be completed at least 14 days before Screening.</t>
+          <t>Participants with a history of rock-joint or brain wobbles within the last 5 years.</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -4370,13 +4370,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J64" s="4" t="inlineStr">
+      <c r="J64" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.01</v>
+        <v>0.1518</v>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
@@ -4417,42 +4417,26 @@
       <c r="E65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Bulleted list of lay terminology summarizing lifestyle considerations including meal requirements, caffeeine, alcohol, tobacco, and activity&gt;</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>LIST</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>You will be asked about any changes in your health or over-the-counter or prescription medicines, vitamins or herbs you have taken since your last visit.</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>NOT FOUND IN PIPELINE</t>
         </is>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.0245</v>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>QA present in Pipeline</t>
+        <v>0</v>
+      </c>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>MISSING from Pipeline</t>
         </is>
       </c>
     </row>
@@ -4487,26 +4471,26 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>KEYVALUE</t>
+          <t>LIST</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>During the repeat-dose phase:</t>
-        </is>
-      </c>
-      <c r="I66" s="4" t="inlineStr">
+          <t>the single ascending dose (SAD) portion of the study</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL (&gt;=70%)</t>
         </is>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.4516</v>
+        <v>0.7294</v>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
@@ -4560,7 +4544,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Daily assessments tailored to the study protocol, including additional biomarker sampling where applicable.</t>
+          <t>Medical history review</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -4568,13 +4552,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J67" s="4" t="inlineStr">
+      <c r="J67" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.2146</v>
+        <v>0.3259</v>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
@@ -4623,7 +4607,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>If you qualify for the study, you will return to the clinic within 35 days for the Study Period.</t>
+          <t>35 days</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -4631,13 +4615,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.1359</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
@@ -4686,21 +4670,21 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Adverse psychiatric and neurological effects observed in Phase 3 clinical studies of blorp inductors.</t>
-        </is>
-      </c>
-      <c r="I69" s="4" t="inlineStr">
+          <t>Health assessment including vital signs (blood pressure, pulse rate, respiratory rate, body temperature).</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J69" s="4" t="inlineStr">
+      <c r="J69" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.253</v>
+        <v>0.4981</v>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
@@ -4750,7 +4734,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>You will be asked questions to be sure that you still qualify for this study.</t>
+          <t>This is a research study and your participation is voluntary</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
@@ -4758,13 +4742,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J70" s="4" t="inlineStr">
+      <c r="J70" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.0228</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
@@ -4800,12 +4784,12 @@
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="5" t="inlineStr">
+      <c r="I71" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J71" s="4" t="inlineStr">
+      <c r="J71" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -4814,7 +4798,7 @@
         <v>0</v>
       </c>
       <c r="L71" s="2" t="inlineStr"/>
-      <c r="M71" s="4" t="inlineStr">
+      <c r="M71" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -4851,26 +4835,26 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>KEYVALUE</t>
+          <t>PARAGRAPH</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>You will be given a signed and dated copy of this consent form to keep.</t>
-        </is>
-      </c>
-      <c r="I72" s="3" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
+          <t>Participants will undergo Check-out procedures on Day 8 after completing the in-residence period at the Clinical Research Unit (CRU). This marks the transition from the in-residence phase to follow-up visits.</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.2712</v>
+        <v>0.3608</v>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
@@ -4921,7 +4905,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>You will be asked about any changes in your health or over-the-counter or prescription medicines, vitamins or herbs you have taken since your last visit.</t>
+          <t>The study drug is “investigational”</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -4929,13 +4913,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J73" s="4" t="inlineStr">
+      <c r="J73" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.289</v>
+        <v>0.2167</v>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
@@ -4974,12 +4958,12 @@
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" s="5" t="inlineStr">
+      <c r="I74" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J74" s="4" t="inlineStr">
+      <c r="J74" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -4988,7 +4972,7 @@
         <v>0</v>
       </c>
       <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="4" t="inlineStr">
+      <c r="M74" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -5026,7 +5010,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>12-lead ECGVital sign monitoring including blood pressure, pulse rate, respiratory rate, and body temperatureClinical laboratory tests (chemistry, hematology, lipid profile, cytokine assessments)Physical examinationsMental health assessmentMonitoring of adverse events and concomitant medication use.</t>
+          <t>Safety measurements such as 12-lead ECG, vital sign monitoring (blood pressure, pulse rate, respiratory rate, and body temperature), and clinical laboratory tests (chemistry, hematology, lipid profile, cytokine assessments).</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -5034,13 +5018,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J75" s="4" t="inlineStr">
+      <c r="J75" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.0707</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
@@ -5076,12 +5060,12 @@
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr"/>
-      <c r="I76" s="5" t="inlineStr">
+      <c r="I76" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J76" s="4" t="inlineStr">
+      <c r="J76" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -5090,7 +5074,7 @@
         <v>0</v>
       </c>
       <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="4" t="inlineStr">
+      <c r="M76" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -5137,7 +5121,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Daily assessments tailored to the study protocol, including additional biomarker sampling where applicable.</t>
+          <t>Medical history review</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -5145,13 +5129,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J77" s="4" t="inlineStr">
+      <c r="J77" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.2146</v>
+        <v>0.3259</v>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
@@ -5200,7 +5184,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>If you qualify for the study, you will return to the clinic within 35 days for the Study Period.</t>
+          <t>35 days</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
@@ -5208,13 +5192,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.1359</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
@@ -5263,21 +5247,21 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Adverse psychiatric and neurological effects observed in Phase 3 clinical studies of blorp inductors.</t>
-        </is>
-      </c>
-      <c r="I79" s="4" t="inlineStr">
+          <t>The study design includes a single ascending dose (SAD) component, which is double-blind, randomized, and placebo-controlled, involving up to six cohorts of healthy participants</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J79" s="4" t="inlineStr">
+      <c r="J79" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.3008</v>
+        <v>0.2422</v>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
@@ -5319,12 +5303,12 @@
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="5" t="inlineStr">
+      <c r="I80" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J80" s="4" t="inlineStr">
+      <c r="J80" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -5333,7 +5317,7 @@
         <v>0</v>
       </c>
       <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="4" t="inlineStr">
+      <c r="M80" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -5362,12 +5346,12 @@
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="5" t="inlineStr">
+      <c r="I81" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J81" s="4" t="inlineStr">
+      <c r="J81" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -5376,7 +5360,7 @@
         <v>0</v>
       </c>
       <c r="L81" s="2" t="inlineStr"/>
-      <c r="M81" s="4" t="inlineStr">
+      <c r="M81" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -5405,12 +5389,12 @@
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="I82" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J82" s="4" t="inlineStr">
+      <c r="J82" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -5419,7 +5403,7 @@
         <v>0</v>
       </c>
       <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="4" t="inlineStr">
+      <c r="M82" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -5450,12 +5434,12 @@
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="5" t="inlineStr">
+      <c r="I83" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J83" s="4" t="inlineStr">
+      <c r="J83" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -5464,7 +5448,7 @@
         <v>0</v>
       </c>
       <c r="L83" s="2" t="inlineStr"/>
-      <c r="M83" s="4" t="inlineStr">
+      <c r="M83" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -5485,12 +5469,12 @@
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="5" t="inlineStr">
+      <c r="I84" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J84" s="4" t="inlineStr">
+      <c r="J84" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -5499,7 +5483,7 @@
         <v>0</v>
       </c>
       <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="4" t="inlineStr">
+      <c r="M84" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -5533,31 +5517,31 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>&lt;second Check-in/Day X&gt;</t>
+          <t>&lt;Second Check-in/Day X&gt;</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>KEYVALUE</t>
+          <t>PARAGRAPH</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>It may take weeks or months after being infected with HIV for the test to be positive. The HIV test is not always right.</t>
-        </is>
-      </c>
-      <c r="I85" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
+          <t>Participants will return for their second Check-in, scheduled for Day X, where evaluations and procedures as outlined in the Schedule of Assessments (SoA) will be conducted. This includes follow-up assessments to monitor the effects of the study intervention and ensure participant safety.</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0.0648</v>
+        <v>0.2112</v>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
@@ -5598,31 +5582,31 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>&lt;second Check-in/Day X&gt;</t>
+          <t>&lt;Second Check-in/Day X&gt;</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>KEYVALUE</t>
+          <t>PARAGRAPH</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>It may take weeks or months after being infected with HIV for the test to be positive. The HIV test is not always right.</t>
-        </is>
-      </c>
-      <c r="I86" s="4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
+          <t>Participants will return for their second Check-in, scheduled for Day X, where evaluations and procedures as outlined in the Schedule of Assessments (SoA) will be conducted. This includes follow-up assessments to monitor the effects of the study intervention and ensure participant safety.</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.1467</v>
+        <v>0.1442</v>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
@@ -5671,21 +5655,21 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Adverse psychiatric and neurological effects observed in Phase 3 clinical studies of blorp inductors.</t>
-        </is>
-      </c>
-      <c r="I87" s="4" t="inlineStr">
+          <t>The study aims to evaluate the safety, pharmacodynamics, and pharmacokinetics of the investigational medicinal product ABC-123</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J87" s="4" t="inlineStr">
+      <c r="J87" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0.1783</v>
+        <v>0.2686</v>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
@@ -5742,7 +5726,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Nonphysical risks: Your sample and data will be kept in a secure location, and every effort will be made to protect any information about you. While it is unlikely, it is possible that information about your DNA could be made known.</t>
+          <t>Blood sampling for exploratory PD and safety biomarkers.</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
@@ -5750,13 +5734,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J88" s="4" t="inlineStr">
+      <c r="J88" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.0385</v>
+        <v>0.1264</v>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
@@ -5792,12 +5776,12 @@
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="5" t="inlineStr">
+      <c r="I89" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J89" s="4" t="inlineStr">
+      <c r="J89" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -5806,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="L89" s="2" t="inlineStr"/>
-      <c r="M89" s="4" t="inlineStr">
+      <c r="M89" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -5848,7 +5832,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Address Line 2</t>
+          <t>Following Check-out from the Clinical Research Unit (CRU), all participants will return for Follow-up study visits up to 6 weeks post dosing in the first three cohorts and 10 weeks post dosing in the remaining cohorts.</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
@@ -5856,13 +5840,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J90" s="4" t="inlineStr">
+      <c r="J90" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0.2286</v>
+        <v>0.1339</v>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
@@ -5916,7 +5900,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Levitation.</t>
+          <t>Participants may benefit from medical evaluations and assessments associated with the study procedures</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
@@ -5924,13 +5908,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL (&gt;=70%)</t>
         </is>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.1081</v>
+        <v>0.7477</v>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
@@ -5969,12 +5953,12 @@
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr"/>
-      <c r="I92" s="5" t="inlineStr">
+      <c r="I92" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J92" s="4" t="inlineStr">
+      <c r="J92" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -5983,7 +5967,7 @@
         <v>0</v>
       </c>
       <c r="L92" s="2" t="inlineStr"/>
-      <c r="M92" s="4" t="inlineStr">
+      <c r="M92" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -6021,7 +6005,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>12-lead ECGVital sign monitoring including blood pressure, pulse rate, respiratory rate, and body temperatureClinical laboratory tests (chemistry, hematology, lipid profile, cytokine assessments)Physical examinationsMental health assessmentMonitoring of adverse events and concomitant medication use.</t>
+          <t>Safety measurements such as 12-lead ECG, vital sign monitoring (blood pressure, pulse rate, respiratory rate, and body temperature), and clinical laboratory tests (chemistry, hematology, lipid profile, cytokine assessments).</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
@@ -6029,13 +6013,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J93" s="4" t="inlineStr">
+      <c r="J93" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0.0707</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
@@ -6087,21 +6071,21 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Although the study drug, ABC-123, has not been shown to get into the brain, you will be closely monitored for the following side effects that have been seen when taking a similar type of drug that do get into the brain:</t>
-        </is>
-      </c>
-      <c r="I94" s="4" t="inlineStr">
+          <t>During the repeat-dose phase</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J94" s="4" t="inlineStr">
+      <c r="J94" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0.1708</v>
+        <v>0.2326</v>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
@@ -6153,21 +6137,21 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Although the study drug, ABC-123, has not been shown to get into the brain, you will be closely monitored for the following side effects that have been seen when taking a similar type of drug that do get into the brain:</t>
-        </is>
-      </c>
-      <c r="I95" s="4" t="inlineStr">
+          <t>During the repeat-dose phase</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J95" s="4" t="inlineStr">
+      <c r="J95" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0.1708</v>
+        <v>0.2326</v>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
@@ -6203,12 +6187,12 @@
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr"/>
-      <c r="I96" s="5" t="inlineStr">
+      <c r="I96" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J96" s="4" t="inlineStr">
+      <c r="J96" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -6217,7 +6201,7 @@
         <v>0</v>
       </c>
       <c r="L96" s="2" t="inlineStr"/>
-      <c r="M96" s="4" t="inlineStr">
+      <c r="M96" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -6259,21 +6243,21 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Risks:</t>
-        </is>
-      </c>
-      <c r="I97" s="4" t="inlineStr">
+          <t>local regulatory authority</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
@@ -6322,21 +6306,21 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Risks:</t>
-        </is>
-      </c>
-      <c r="I98" s="4" t="inlineStr">
+          <t>local regulatory authority</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
@@ -6364,12 +6348,12 @@
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr"/>
-      <c r="I99" s="5" t="inlineStr">
+      <c r="I99" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J99" s="4" t="inlineStr">
+      <c r="J99" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -6378,7 +6362,7 @@
         <v>0</v>
       </c>
       <c r="L99" s="2" t="inlineStr"/>
-      <c r="M99" s="4" t="inlineStr">
+      <c r="M99" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -6399,12 +6383,12 @@
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="5" t="inlineStr">
+      <c r="I100" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J100" s="4" t="inlineStr">
+      <c r="J100" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -6413,7 +6397,7 @@
         <v>0</v>
       </c>
       <c r="L100" s="2" t="inlineStr"/>
-      <c r="M100" s="4" t="inlineStr">
+      <c r="M100" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -6455,21 +6439,21 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>This study drug is intended to treat patients with boneitis (a disease that causes bones to change shape or disappear).</t>
-        </is>
-      </c>
-      <c r="I101" s="4" t="inlineStr">
+          <t>boneitis</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.126</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
@@ -6505,12 +6489,12 @@
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="5" t="inlineStr">
+      <c r="I102" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J102" s="4" t="inlineStr">
+      <c r="J102" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -6519,7 +6503,7 @@
         <v>0</v>
       </c>
       <c r="L102" s="2" t="inlineStr"/>
-      <c r="M102" s="4" t="inlineStr">
+      <c r="M102" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -6557,21 +6541,21 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>selected contract research organizations (CRO) is being paid by the Sponsor (the company paying for this study) to conduct this research study.</t>
-        </is>
-      </c>
-      <c r="I103" s="4" t="inlineStr">
+          <t>selected contract research organizations (CRO)</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J103" s="4" t="inlineStr">
+      <c r="J103" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.3619</v>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
@@ -6599,12 +6583,12 @@
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr"/>
-      <c r="I104" s="5" t="inlineStr">
+      <c r="I104" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J104" s="4" t="inlineStr">
+      <c r="J104" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -6613,7 +6597,7 @@
         <v>0</v>
       </c>
       <c r="L104" s="2" t="inlineStr"/>
-      <c r="M104" s="4" t="inlineStr">
+      <c r="M104" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -6642,12 +6626,12 @@
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr"/>
-      <c r="I105" s="5" t="inlineStr">
+      <c r="I105" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J105" s="4" t="inlineStr">
+      <c r="J105" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -6656,7 +6640,7 @@
         <v>0</v>
       </c>
       <c r="L105" s="2" t="inlineStr"/>
-      <c r="M105" s="4" t="inlineStr">
+      <c r="M105" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -6685,12 +6669,12 @@
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr"/>
-      <c r="I106" s="5" t="inlineStr">
+      <c r="I106" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J106" s="4" t="inlineStr">
+      <c r="J106" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -6699,7 +6683,7 @@
         <v>0</v>
       </c>
       <c r="L106" s="2" t="inlineStr"/>
-      <c r="M106" s="4" t="inlineStr">
+      <c r="M106" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -6737,21 +6721,21 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>selected contract research organizations (CRO) is being paid by the Sponsor (the company paying for this study) to conduct this research study.</t>
-        </is>
-      </c>
-      <c r="I107" s="4" t="inlineStr">
+          <t>selected contract research organizations (CRO)</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J107" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL (&gt;=70%)</t>
         </is>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0.4022</v>
+        <v>0.878</v>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
@@ -6779,12 +6763,12 @@
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr"/>
-      <c r="I108" s="5" t="inlineStr">
+      <c r="I108" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J108" s="4" t="inlineStr">
+      <c r="J108" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -6793,7 +6777,7 @@
         <v>0</v>
       </c>
       <c r="L108" s="2" t="inlineStr"/>
-      <c r="M108" s="4" t="inlineStr">
+      <c r="M108" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -6822,12 +6806,12 @@
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" s="5" t="inlineStr">
+      <c r="I109" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J109" s="4" t="inlineStr">
+      <c r="J109" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -6836,7 +6820,7 @@
         <v>0</v>
       </c>
       <c r="L109" s="2" t="inlineStr"/>
-      <c r="M109" s="4" t="inlineStr">
+      <c r="M109" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -6876,7 +6860,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>In animal studies, there were no side effects observed at doses approximately 318-fold larger than the highest dose you could receive in this study.</t>
+          <t>318-fold</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
@@ -6884,13 +6868,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0.1026</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
@@ -6924,12 +6908,12 @@
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr"/>
-      <c r="I111" s="5" t="inlineStr">
+      <c r="I111" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J111" s="4" t="inlineStr">
+      <c r="J111" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -6938,7 +6922,7 @@
         <v>0</v>
       </c>
       <c r="L111" s="2" t="inlineStr"/>
-      <c r="M111" s="4" t="inlineStr">
+      <c r="M111" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -6981,18 +6965,18 @@
           <t>Because this drug is investigational, all of its side effects may not be known. There may be rare and unknown side effects. Some of these may be life threatening.</t>
         </is>
       </c>
-      <c r="I112" s="4" t="inlineStr">
+      <c r="I112" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J112" s="4" t="inlineStr">
+      <c r="J112" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0.3397</v>
+        <v>0.3833</v>
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
@@ -7039,21 +7023,21 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Tell the study staff about any side effects or problems.</t>
-        </is>
-      </c>
-      <c r="I113" s="4" t="inlineStr">
+          <t>ABC-123 has not been given to humans, so no information about side effects are available.</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J113" s="4" t="inlineStr">
+      <c r="J113" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0.2621</v>
+        <v>0.3063</v>
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
@@ -7103,18 +7087,18 @@
           <t>If you do not understand what any of these side effects mean, please ask the study doctor or study staff to explain these terms to you.</t>
         </is>
       </c>
-      <c r="I114" s="4" t="inlineStr">
+      <c r="I114" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J114" s="4" t="inlineStr">
+      <c r="J114" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.0473</v>
+        <v>0.2875</v>
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
@@ -7161,21 +7145,21 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>A rare but possible side effect of lidocaine is an extreme allergic reaction. These symptoms may include:</t>
-        </is>
-      </c>
-      <c r="I115" s="4" t="inlineStr">
+          <t>ABC-123 has not been given to humans, so no information about side effects are available.</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J115" s="4" t="inlineStr">
+      <c r="J115" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0.2312</v>
+        <v>0.303</v>
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
@@ -7209,12 +7193,12 @@
       <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr"/>
-      <c r="I116" s="5" t="inlineStr">
+      <c r="I116" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J116" s="4" t="inlineStr">
+      <c r="J116" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -7223,7 +7207,7 @@
         <v>0</v>
       </c>
       <c r="L116" s="2" t="inlineStr"/>
-      <c r="M116" s="4" t="inlineStr">
+      <c r="M116" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -7263,21 +7247,21 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>A rare but possible side effect of lidocaine is an extreme allergic reaction. These symptoms may include:</t>
-        </is>
-      </c>
-      <c r="I117" s="4" t="inlineStr">
+          <t>ABC-123 has not been given to humans, so no information about side effects are available.</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J117" s="4" t="inlineStr">
+      <c r="J117" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0.2312</v>
+        <v>0.303</v>
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
@@ -7327,18 +7311,18 @@
           <t>If you do not understand what any of these side effects mean, please ask the study doctor or study staff to explain these terms to you.</t>
         </is>
       </c>
-      <c r="I118" s="4" t="inlineStr">
+      <c r="I118" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J118" s="4" t="inlineStr">
+      <c r="J118" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.052</v>
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
@@ -7388,18 +7372,18 @@
           <t>Because this drug is investigational, all of its side effects may not be known. There may be rare and unknown side effects. Some of these may be life threatening.</t>
         </is>
       </c>
-      <c r="I119" s="4" t="inlineStr">
+      <c r="I119" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J119" s="4" t="inlineStr">
+      <c r="J119" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0.3324</v>
+        <v>0.3697</v>
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
@@ -7446,21 +7430,21 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>You must tell the study doctor or study staff about all side effects that you have. If you are not honest about your side effects, you may harm yourself by staying in this study. The study staff will continue to follow up if you have side effects that are still present at the end of the study.</t>
-        </is>
-      </c>
-      <c r="I120" s="4" t="inlineStr">
+          <t>ABC-123 has not been given to humans, so no information about side effects are available.</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J120" s="4" t="inlineStr">
+      <c r="J120" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0.2584</v>
+        <v>0.3348</v>
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
@@ -7506,42 +7490,26 @@
         </is>
       </c>
       <c r="E121" s="2" t="n"/>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Bullet list of lay terminology summarizing the protocol criteria for women to be not considered a WOCBP&gt;</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>LIST</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>or call toll free:XXX-XXX-XXXX</t>
-        </is>
-      </c>
-      <c r="I121" s="3" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J121" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="F121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr"/>
+      <c r="I121" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J121" s="5" t="inlineStr">
+        <is>
+          <t>NOT FOUND IN PIPELINE</t>
         </is>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0.0073</v>
-      </c>
-      <c r="L121" s="2" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="M121" s="2" t="inlineStr">
-        <is>
-          <t>QA present in Pipeline</t>
+        <v>0</v>
+      </c>
+      <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="5" t="inlineStr">
+        <is>
+          <t>MISSING from Pipeline</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7547,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>VOLUNTEERING TO BE IN THE STUDY</t>
+          <t>Females undergoing hormone replacement therapy (HRT) and with uncertain menopausal status must utilize non-estrogen hormonal contraception methods to continue their HRT during the study. Alternatively, they may need to discontinue HRT to confirm their postmenopausal status before enrollment.</t>
         </is>
       </c>
       <c r="I122" s="3" t="inlineStr">
@@ -7587,13 +7555,13 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="J122" s="4" t="inlineStr">
+      <c r="J122" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0.0193</v>
+        <v>0.2972</v>
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
@@ -7640,21 +7608,21 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>The study doctor, the sponsor company, appropriate IRB/IEC members, or the FDA may take you out of the study without your permission, at any time, for the following reasons:</t>
-        </is>
-      </c>
-      <c r="I123" s="4" t="inlineStr">
+          <t>Male participants are required to use contraception while undergoing the study intervention and for a period of at least 6 months following the final dose. This includes the use of a male condom with spermicide alongside an additional acceptable method of contraception. Moreover, sexual intercourse with pregnant or breastfeeding female partners should be avoided unless condoms are used during this timeframe.</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J123" s="4" t="inlineStr">
+      <c r="J123" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0.0492</v>
+        <v>0.2602</v>
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
@@ -7693,26 +7661,38 @@
         </is>
       </c>
       <c r="E124" s="2" t="n"/>
-      <c r="F124" s="2" t="inlineStr"/>
-      <c r="G124" s="2" t="inlineStr"/>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Bullet list of lay terminology summarizing the protocol listed acceptable second methods of contraception.&gt;</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>LIST</t>
+        </is>
+      </c>
       <c r="H124" s="2" t="inlineStr"/>
-      <c r="I124" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>NOT FOUND IN PIPELINE</t>
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>BOTH EMPTY</t>
         </is>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="2" t="inlineStr"/>
-      <c r="M124" s="4" t="inlineStr">
-        <is>
-          <t>MISSING from Pipeline</t>
+        <v>1</v>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>UNRESOLVED</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>QA present in Pipeline</t>
         </is>
       </c>
     </row>
@@ -7739,26 +7719,42 @@
         </is>
       </c>
       <c r="E125" s="2" t="n"/>
-      <c r="F125" s="2" t="inlineStr"/>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr"/>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Lay terminology summarizing pregnancy information collection practices for male participants with partners who become pregnant.&gt;</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>PARAGRAPH</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>For male participants whose partners become pregnant during the study, the Investigator will collect relevant pregnancy information. This will include obtaining signed informed consent from the pregnant partner and recording details on the appropriate form. The information will be submitted to the Sponsor within 24 hours of learning about the pregnancy. Follow-up will be conducted to determine the pregnancy outcome, including the health status of the mother and child, which will be reported to the Sponsor. Generally, follow-up will extend up to 6 to 8 weeks after the estimated delivery date. Any pregnancy termination will also be documented, regardless of fetal status or reason for the procedure.</t>
+        </is>
+      </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J125" s="4" t="inlineStr">
-        <is>
-          <t>NOT FOUND IN PIPELINE</t>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J125" s="5" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="2" t="inlineStr"/>
-      <c r="M125" s="4" t="inlineStr">
-        <is>
-          <t>MISSING from Pipeline</t>
+        <v>0.0264</v>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>QA present in Pipeline</t>
         </is>
       </c>
     </row>
@@ -7799,21 +7795,21 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Please answer YES or NO to the following questions:</t>
-        </is>
-      </c>
-      <c r="I126" s="4" t="inlineStr">
+          <t>Female participants who become pregnant during the study will cease receiving the study intervention. The Investigator will monitor the pregnancy to determine its outcome, collecting relevant follow-up information about both the participant and the neonate. This data will be shared with the Sponsor. Typically, follow-up will conclude within 6 to 8 weeks after the expected delivery date. Any pregnancy terminations will be documented, regardless of the fetal condition or the reasons for the procedure. Serious adverse events (SAEs) related to the pregnancy and considered connected to the study intervention by the Investigator will be reported to the Sponsor, although the Investigator is not required to actively seek such information from former participants.</t>
+        </is>
+      </c>
+      <c r="I126" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J126" s="4" t="inlineStr">
+      <c r="J126" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0.0043</v>
+        <v>0.0935</v>
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
@@ -7860,21 +7856,21 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>This consent form contains important information to help you decide if you want to be in the study. If you have any questions that are not answered in this consent form, ask one of the study staff.</t>
-        </is>
-      </c>
-      <c r="I127" s="4" t="inlineStr">
+          <t>boneitis</t>
+        </is>
+      </c>
+      <c r="I127" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J127" s="4" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>LOW SIMILARITY</t>
         </is>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0.1101</v>
+        <v>0.5517</v>
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
@@ -7921,21 +7917,21 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Stendarr, Inc. IRB</t>
-        </is>
-      </c>
-      <c r="I128" s="4" t="inlineStr">
+          <t>Stendarr, Inc.</t>
+        </is>
+      </c>
+      <c r="I128" s="5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="J128" s="4" t="inlineStr">
+      <c r="J128" s="5" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0.36</v>
+        <v>0.2609</v>
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
@@ -7961,12 +7957,12 @@
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr"/>
-      <c r="I129" s="5" t="inlineStr">
+      <c r="I129" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J129" s="4" t="inlineStr">
+      <c r="J129" s="5" t="inlineStr">
         <is>
           <t>NOT FOUND IN PIPELINE</t>
         </is>
@@ -7975,7 +7971,7 @@
         <v>0</v>
       </c>
       <c r="L129" s="2" t="inlineStr"/>
-      <c r="M129" s="4" t="inlineStr">
+      <c r="M129" s="5" t="inlineStr">
         <is>
           <t>MISSING from Pipeline</t>
         </is>
@@ -7999,10 +7995,10 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>(Study Doctor)Medical Investigator</t>
-        </is>
-      </c>
-      <c r="I130" s="5" t="inlineStr">
+          <t>Medical Investigator</t>
+        </is>
+      </c>
+      <c r="I130" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8044,10 +8040,10 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Medical Investigator                     Stendarr, Inc. IRB Approved Version DD Mon YYYY</t>
-        </is>
-      </c>
-      <c r="I131" s="5" t="inlineStr">
+          <t>Medical Investigator</t>
+        </is>
+      </c>
+      <c r="I131" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8089,10 +8085,10 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Medical Investigator                     Stendarr, Inc. IRB Approved Version DD Mon YYYY</t>
-        </is>
-      </c>
-      <c r="I132" s="5" t="inlineStr">
+          <t>Medical Investigator</t>
+        </is>
+      </c>
+      <c r="I132" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8134,10 +8130,10 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Compensation (amount)</t>
-        </is>
-      </c>
-      <c r="I133" s="5" t="inlineStr">
+          <t>Medical Investigator</t>
+        </is>
+      </c>
+      <c r="I133" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8179,10 +8175,10 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Follow-Up Period</t>
-        </is>
-      </c>
-      <c r="I134" s="5" t="inlineStr">
+          <t>Medical Investigator</t>
+        </is>
+      </c>
+      <c r="I134" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8227,7 +8223,7 @@
           <t>(where possible, 3 telephone calls and, if necessary, a certified letter to the participant’s last known mailing address or local equivalent methods)</t>
         </is>
       </c>
-      <c r="I135" s="5" t="inlineStr">
+      <c r="I135" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8269,10 +8265,10 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>The study design includes a single ascending dose (SAD) component, which is double-blind, randomized, and placebo-controlled, involving up to six cohorts of healthy participants.</t>
-        </is>
-      </c>
-      <c r="I136" s="5" t="inlineStr">
+          <t>ABC-123</t>
+        </is>
+      </c>
+      <c r="I136" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8314,10 +8310,10 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>No serious adverse effects were observed in blorp knockout mice, supporting the general safety of blorp inductors.</t>
-        </is>
-      </c>
-      <c r="I137" s="5" t="inlineStr">
+          <t>ABC-123</t>
+        </is>
+      </c>
+      <c r="I137" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8359,10 +8355,10 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>HOW LONG THE STUDY WILL LAST AND WHO WILL BE IN THE STUDY</t>
-        </is>
-      </c>
-      <c r="I138" s="5" t="inlineStr">
+          <t>ABC-123</t>
+        </is>
+      </c>
+      <c r="I138" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8404,10 +8400,10 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>Study Procedures Check-in/Day 1</t>
-        </is>
-      </c>
-      <c r="I139" s="5" t="inlineStr">
+          <t>ABC-123</t>
+        </is>
+      </c>
+      <c r="I139" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8449,10 +8445,10 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>The sponsor would like to keep the blood samples collected in the course of the study for future research to continue analyzing it for genes involved in the safety, pharmacokinetics (what the body does to a drug) and pharmacodynamics (how a medicine acts in the body) of the study drug, ABC-123. This information may be useful in increasing the knowledge of differences among individuals in the way they metabolize the investigational product as well as helping in the development of new drugs or improvement of existing drugs. You will not have any right to any such products or inventions or be entitled to any financial benefits from any such products. The information may be published or used for regulatory filings, but your identity will never be disclosed.</t>
-        </is>
-      </c>
-      <c r="I140" s="5" t="inlineStr">
+          <t>ABC-123</t>
+        </is>
+      </c>
+      <c r="I140" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8494,10 +8490,10 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>ABC-123 has not been given to humans, so no information about side effects are available.</t>
-        </is>
-      </c>
-      <c r="I141" s="5" t="inlineStr">
+          <t>ABC-123</t>
+        </is>
+      </c>
+      <c r="I141" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8539,10 +8535,10 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>Non-Physical Risks Associated with the Planned Genetic Analysis and Future Research of Biomarker Samples:</t>
-        </is>
-      </c>
-      <c r="I142" s="5" t="inlineStr">
+          <t>ABC-123</t>
+        </is>
+      </c>
+      <c r="I142" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8584,10 +8580,10 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>Be aware that this Federal law does not protect you against genetic discrimination by companies that sell life insurance, disability insurance, or long term-care insurance, nor does it prohibit discrimination based on a genetic disease or disorder that you already know about.</t>
-        </is>
-      </c>
-      <c r="I143" s="5" t="inlineStr">
+          <t>ABC-123</t>
+        </is>
+      </c>
+      <c r="I143" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8629,10 +8625,10 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Risks of Subcutaneous (SC) Injection:</t>
-        </is>
-      </c>
-      <c r="I144" s="5" t="inlineStr">
+          <t>ABC-123</t>
+        </is>
+      </c>
+      <c r="I144" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8674,10 +8670,10 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>If you participate in the repeat-dose portion of the study, the study should take about 1 week of your time and you will be given a subcutaneous injection of ABC-123 or placebo every other week for 3 doses.</t>
-        </is>
-      </c>
-      <c r="I145" s="5" t="inlineStr">
+          <t>the repeat-dose portion of the study</t>
+        </is>
+      </c>
+      <c r="I145" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8719,10 +8715,10 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>You cannot be in this study if you meet any of the following criteria:</t>
-        </is>
-      </c>
-      <c r="I146" s="5" t="inlineStr">
+          <t>the repeat-dose portion of the study</t>
+        </is>
+      </c>
+      <c r="I146" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8764,10 +8760,10 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>Screening</t>
-        </is>
-      </c>
-      <c r="I147" s="5" t="inlineStr">
+          <t>the repeat-dose portion of the study</t>
+        </is>
+      </c>
+      <c r="I147" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8809,10 +8805,10 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>KEY INFORMATION</t>
-        </is>
-      </c>
-      <c r="I148" s="5" t="inlineStr">
+          <t>the repeat-dose portion of the study</t>
+        </is>
+      </c>
+      <c r="I148" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8854,10 +8850,10 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>the single ascending dose (SAD) portion of the study, involving cohorts of healthy participants:</t>
-        </is>
-      </c>
-      <c r="I149" s="5" t="inlineStr">
+          <t>the repeat-dose portion of the study</t>
+        </is>
+      </c>
+      <c r="I149" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8899,10 +8895,10 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>You must be of non-childbearing potential (not able to have children) to be in this study. This includes:</t>
-        </is>
-      </c>
-      <c r="I150" s="5" t="inlineStr">
+          <t>the repeat-dose portion of the study</t>
+        </is>
+      </c>
+      <c r="I150" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8944,10 +8940,10 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>If you are enrolled in the repeat-dose portion of the study you may benefit from ABC-123 for your boneitis.</t>
-        </is>
-      </c>
-      <c r="I151" s="5" t="inlineStr">
+          <t>the repeat-dose portion of the study</t>
+        </is>
+      </c>
+      <c r="I151" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8989,10 +8985,10 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>IF YOU ANSWERED “NO” TO ANY OF THE ABOVE QUESTIONS, OR YOU ARE UNABLE TO ANSWER ANY OF THE ABOVE QUESTIONS,</t>
-        </is>
-      </c>
-      <c r="I152" s="5" t="inlineStr">
+          <t>the repeat-dose portion of the study</t>
+        </is>
+      </c>
+      <c r="I152" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9034,10 +9030,10 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>If you are injured from your participation in this study, you should contact the study doctor as soon as possible in person or at the telephone number listed on page one of this consent form. Medical care may be obtained in the same way you would ordinarily obtain other medical treatment. If you suffer a physical injury that is directly caused by the study drug given as described in the study protocol or by a properly performed medical procedure required by the protocol, the reasonable costs of necessary medical treatment of the injury will be reimbursed by the Sponsor to the extent these costs are not covered by your insurance or other third-party coverage.</t>
-        </is>
-      </c>
-      <c r="I153" s="5" t="inlineStr">
+          <t>the repeat-dose portion of the study</t>
+        </is>
+      </c>
+      <c r="I153" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9079,10 +9075,10 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>Participant Responsibilities:</t>
-        </is>
-      </c>
-      <c r="I154" s="5" t="inlineStr">
+          <t>5 mg</t>
+        </is>
+      </c>
+      <c r="I154" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9124,10 +9120,10 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>single ascending dose phase:</t>
-        </is>
-      </c>
-      <c r="I155" s="5" t="inlineStr">
+          <t>318-fold</t>
+        </is>
+      </c>
+      <c r="I155" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9169,10 +9165,10 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>Tell the study doctor or the study staff if you change your mind about staying in the study.</t>
-        </is>
-      </c>
-      <c r="I156" s="5" t="inlineStr">
+          <t>Cohorts 1–6</t>
+        </is>
+      </c>
+      <c r="I156" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9214,10 +9210,10 @@
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>Alcohol consumption is prohibited from 48 hours before Check-in until Check-out from the CRU.</t>
-        </is>
-      </c>
-      <c r="I157" s="5" t="inlineStr">
+          <t>Cohorts 1–6</t>
+        </is>
+      </c>
+      <c r="I157" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9249,7 +9245,7 @@
       <c r="E158" s="2" t="n"/>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>&lt;Bullet list of lay terminology of all assessments required during the follow-up period; note differences in assessments based on the day and cohort of “follow-up period”&gt;</t>
+          <t>&lt;Bulleted list of lay terminology summarizing lifestyle considerations including meal requirements, caffeeine, alcohol, tobacco, and activity&gt;</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -9257,12 +9253,8 @@
           <t>LIST</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>Routine physical examinations and vital sign monitoring, including blood pressure, pulse rate, respiratory rate, and body temperature.12-lead ECG to assess heart function.Clinical laboratory tests, such as blood chemistry, hematology, lipid profile, and cytokine assessments.Mental health evaluations to monitor psychological well-being.Adverse event tracking and recording concomitant medication use.Specific assessments tailored to the day of in-residence, with additional focus on pharmacokinetic and pharmacodynamic sampling as required..</t>
-        </is>
-      </c>
-      <c r="I158" s="5" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr"/>
+      <c r="I158" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9277,7 +9269,7 @@
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>UNRESOLVED</t>
         </is>
       </c>
       <c r="M158" s="6" t="inlineStr">
@@ -9304,10 +9296,10 @@
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>The crunge.</t>
-        </is>
-      </c>
-      <c r="I159" s="5" t="inlineStr">
+          <t>Blood sampling for exploratory PD and safety biomarkers, including up to 3 additional samples per treatment period.</t>
+        </is>
+      </c>
+      <c r="I159" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9339,7 +9331,7 @@
       <c r="E160" s="2" t="n"/>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>&lt;Bullet list of lay terminology of all assessments required during the first in-residence period; note differences in assessments based on the day of “in-residence”&gt;</t>
+          <t>&lt;Bullet list of lay terminology of all assessments required during the follow-up period; note differences in assessments based on the day and cohort of “follow-up period”&gt;</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -9349,10 +9341,10 @@
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>Blood sampling for exploratory PD and safety biomarkers, including up to 3 additional samples per treatment period.Monitoring of liver enzyme levels (ALT, AST) and other hepatic indicators as per the Schedule of Assessments.Physical examinations and detailed history taking for participants with elevated liver enzymes (&gt;3 × ULN).Laboratory tests including ALT, AST, bilirubin levels, alkaline phosphatase, and gamma glutamyltransferase.Liver ultrasound and tests for acetaminophen toxicity and viral hepatitis causes if indicated..</t>
-        </is>
-      </c>
-      <c r="I160" s="5" t="inlineStr">
+          <t>Blood sampling for exploratory PD and safety biomarkers, including up to 3 additional samples per treatment period.</t>
+        </is>
+      </c>
+      <c r="I160" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9384,20 +9376,20 @@
       <c r="E161" s="2" t="n"/>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>&lt;First Check-out/Day X&gt;</t>
+          <t>&lt;Bullet list of lay terminology of all assessments required during the first in-residence period; note differences in assessments based on the day of “in-residence”&gt;</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>PARAGRAPH</t>
+          <t>LIST</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>The following will be done if you leave the study early:</t>
-        </is>
-      </c>
-      <c r="I161" s="5" t="inlineStr">
+          <t>Routine physical examinations and vital sign monitoring, including blood pressure, pulse rate, respiratory rate, and body temperature.</t>
+        </is>
+      </c>
+      <c r="I161" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9429,20 +9421,20 @@
       <c r="E162" s="2" t="n"/>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>&lt;first Check-out/Day X&gt;</t>
+          <t>&lt;First Check-out/Day X&gt;</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>KEYVALUE</t>
+          <t>PARAGRAPH</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>Blood samples will be taken by single needle-sticks or by a tube that is left in your arm. You cannot choose how the blood is taken.</t>
-        </is>
-      </c>
-      <c r="I162" s="5" t="inlineStr">
+          <t>Following Check-out from the CRU, all participants will return for Follow-up study visits up to 6 weeks post dosing in the first 3 cohorts and 10 weeks post dosing in the remaining cohorts, as detailed in the Schedule of Assessments.</t>
+        </is>
+      </c>
+      <c r="I162" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9474,20 +9466,20 @@
       <c r="E163" s="2" t="n"/>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>&lt;Bullet list of lay terminology of all assessments required during first Check-out&gt;</t>
+          <t>&lt;first Check-out/Day X&gt;</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>LIST</t>
+          <t>KEYVALUE</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>Vital sign monitoring: Includes measurements of blood pressure, pulse rate, respiratory rate, and body temperature.12-lead ECG: Used to assess heart function.Clinical laboratory tests: Evaluations of chemistry, hematology, lipid profile, and cytokine levels.Physical examinations: Comprehensive health check-ups.Mental health assessments: Evaluations to ensure psychological well-being.Adverse events monitoring: Observations to identify any negative health impacts.Concomitant medication tracking: Documentation of other medications taken during the study..</t>
-        </is>
-      </c>
-      <c r="I163" s="5" t="inlineStr">
+          <t>Following Check-out from the CRU, all participants will return for Follow-up study visits up to 6 weeks post dosing in the first 3 cohorts and 10 weeks post dosing in the remaining cohorts, as detailed in the Schedule of Assessments.</t>
+        </is>
+      </c>
+      <c r="I163" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9519,7 +9511,7 @@
       <c r="E164" s="2" t="n"/>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>&lt;Bullet list of lay terminology of all assessments required during the non-residential period; note differences in assessments based on the days of “non-residential”&gt;</t>
+          <t>&lt;Bullet list of lay terminology of all assessments required during first Check-out&gt;</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -9529,10 +9521,10 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>Physical risks: you may have a sore arm from where the blood sample is taken.</t>
-        </is>
-      </c>
-      <c r="I164" s="5" t="inlineStr">
+          <t>12-lead ECG</t>
+        </is>
+      </c>
+      <c r="I164" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9564,20 +9556,20 @@
       <c r="E165" s="2" t="n"/>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>&lt;state health authority&gt;</t>
+          <t>&lt;Bullet list of lay terminology of all assessments required during the non-residential period; note differences in assessments based on the days of “non-residential”&gt;</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>KEYVALUE</t>
+          <t>LIST</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>Blood Samples (taken by single needle-sticks or by a tube that is left in your arm):</t>
-        </is>
-      </c>
-      <c r="I165" s="5" t="inlineStr">
+          <t>Safety measurements, such as ECG, vital signs, laboratory tests, and physical examinations, will be conducted at specific intervals according to the Schedule of Activities (SoA)</t>
+        </is>
+      </c>
+      <c r="I165" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9609,7 +9601,7 @@
       <c r="E166" s="2" t="n"/>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>&lt;XX years&gt;</t>
+          <t>&lt;state health authority&gt;</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
@@ -9619,10 +9611,10 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>Your DNA sample will be labeled with a code and not with your name or birthday to protect your identity and will be stored in a secure location until it is all used up or 30 years, whichever is sooner. You can ask for your DNA sample to be destroyed at any time and your sample will not be used for any new research, but any research data that has already been generated will not be destroyed.</t>
-        </is>
-      </c>
-      <c r="I166" s="5" t="inlineStr">
+          <t>local regulatory authority</t>
+        </is>
+      </c>
+      <c r="I166" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9664,10 +9656,10 @@
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>The sample will be retained in a secure location until the deoxyribonucleic acid (DNA - the material that determines your unique characteristics such as eye and hair color, and also influences the way your body responds to certain drugs and hereditary disease factors) has been exhausted, until the sponsor instructs the genotyping contractor to destroy the sample in accordance with laboratory procedures, or for 2 years. During this time, the DNA sample will not be immortalized or sold to anyone.</t>
-        </is>
-      </c>
-      <c r="I167" s="5" t="inlineStr">
+          <t>30 years</t>
+        </is>
+      </c>
+      <c r="I167" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9699,7 +9691,7 @@
       <c r="E168" s="2" t="n"/>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>&lt;Firstname Lastname&gt;</t>
+          <t>&lt;XX years&gt;</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
@@ -9709,10 +9701,10 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>Address Line 1</t>
-        </is>
-      </c>
-      <c r="I168" s="5" t="inlineStr">
+          <t>30 years</t>
+        </is>
+      </c>
+      <c r="I168" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9754,10 +9746,10 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>Address Line 1</t>
-        </is>
-      </c>
-      <c r="I169" s="5" t="inlineStr">
+          <t>&lt;Firstname Lastname&gt;</t>
+        </is>
+      </c>
+      <c r="I169" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9789,20 +9781,20 @@
       <c r="E170" s="2" t="n"/>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>&lt;Bullet list of lay terminology summarizing the protocol listed acceptable second methods of contraception.&gt;</t>
+          <t>&lt;Firstname Lastname&gt;</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>LIST</t>
+          <t>KEYVALUE</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>If it becomes harmful to your health</t>
-        </is>
-      </c>
-      <c r="I170" s="5" t="inlineStr">
+          <t>&lt;Firstname Lastname&gt;</t>
+        </is>
+      </c>
+      <c r="I170" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9834,20 +9826,16 @@
       <c r="E171" s="2" t="n"/>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>&lt;Lay terminology summarizing pregnancy information collection practices for male participants with partners who become pregnant.&gt;</t>
+          <t>&lt;Bullet list of lay terminology summarizing the protocol criteria for women to be not considered a WOCBP&gt;</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>PARAGRAPH</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>NEW FINDINGS</t>
-        </is>
-      </c>
-      <c r="I171" s="5" t="inlineStr">
+          <t>LIST</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr"/>
+      <c r="I171" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9862,7 +9850,7 @@
       </c>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>UNRESOLVED</t>
         </is>
       </c>
       <c r="M171" s="6" t="inlineStr">
@@ -9889,10 +9877,10 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>Warmth or drainage</t>
-        </is>
-      </c>
-      <c r="I172" s="5" t="inlineStr">
+          <t>contact@trialstudy.com</t>
+        </is>
+      </c>
+      <c r="I172" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10325,34 +10313,60 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>&lt;Check-out/Day X&gt;</t>
+          <t>&lt;Bulleted list of lay terminology summarizing lifestyle considerations including meal requirements, caffeeine, alcohol, tobacco, and activity&gt;</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>KeyValue</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr"/>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>&lt;li&gt;Do not donate blood from 8 weeks before screening until 90 days after your final follow-up visit.&lt;/li&gt;&lt;li&gt;Do not use tetrahydrocannabinol (THC), cannabidiol (CBD), or other cannabinoids for 14 days before screening through the end of the study.&lt;/li&gt;&lt;li&gt;Complete any planned vaccinations at least 14 days before screening.&lt;/li&gt;&lt;li&gt;Do not take any prescription or nonprescription medications, vitamins (except ongoing multivitamin), minerals, or herbal supplements unless approved by the study doctor (for SAD Cohorts).&lt;/li&gt;&lt;li&gt;If you are in the Repeat-Dose Cohort, keep your boneitis treatment and other allowed medications stable and unchanged unless approved by the study doctor.&lt;/li&gt;&lt;li&gt;Do not ingest caffeine or xanthine-containing products (like coffee, tea, cola, or chocolate) from 24 hours before check-in until check-out from the Clinical Research Unit (CRU).&lt;/li&gt;&lt;li&gt;Do not drink alcohol from 48 hours before check-in until check-out from the CRU.&lt;/li&gt;&lt;li&gt;Do not use tobacco or nicotine-containing products (including nicotine patches) while in the CRU.&lt;/li&gt;</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6 weeks</t>
+          <t>Participants must be willing and able to fast for at least 10 hours prior to fasting laboratory tests. 
+Caffeine, Alcohol, and Tobacco 
+Participants will abstain from ingesting caffeine- or xanthine-containing products (eg, coffee, tea, cola drinks, and chocolate) from 24 hours before Check-in until Check-out from the CRU. 
+Participants will abstain from alcohol from 48 hours before Check-in until Check-out from the CRU. 
+Participants who use tobacco products will be instructed that use of nicotine-containing products (including nicotine patches) will not be permitted while they are in the CRU.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>&lt;Bullet list of lay terminology of all assessments required during the follow-up period; note differences in assessments based on the day and cohort of “follow-up period”&gt;</t>
+          <t>&lt;Check-out/Day X&gt;</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>KeyValue</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr"/>
       <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>6 weeks</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Bullet list of lay terminology of all assessments required during the follow-up period; note differences in assessments based on the day and cohort of “follow-up period”&gt;</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>The Investigator is obligated to perform or arrange for the conduct of supplemental measurements and/or evaluations as medically indicated or as requested by the Sponsor (or designee) to elucidate the nature and/or causality of the AE or SAE as fully as possible. This may include additional laboratory tests or investigations, histopathological examinations, or consultation with other health care professionals. 
 If a participant dies during participation in the study or during a recognized Follow-up period, the Investigator will provide the Sponsor (or designee) with a copy of any post-mortem findings including histopathology. 
@@ -10361,37 +10375,37 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>&lt;lay terminology for repeat-dose portion of study&gt;</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Paragraph</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>The SAD portion of this study is a standard design for first-in-human testing with a monoclonal antibody. In addition, a 4-week repeated dose cohort will allow confirmation of the safety, tolerability, and repeat-dose PK and immunogenicity in the target population prior to proceeding to subsequent repeat-dose studies in a patient population.</t>
-        </is>
-      </c>
-    </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>&lt;Bullet list of lay terminology of all assessments required during the first in-residence period; note differences in assessments based on the day of “in-residence”&gt;</t>
+          <t>&lt;lay terminology for repeat-dose portion of study&gt;</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Paragraph</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr"/>
       <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>The SAD portion of this study is a standard design for first-in-human testing with a monoclonal antibody. In addition, a 4-week repeated dose cohort will allow confirmation of the safety, tolerability, and repeat-dose PK and immunogenicity in the target population prior to proceeding to subsequent repeat-dose studies in a patient population.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Bullet list of lay terminology of all assessments required during the first in-residence period; note differences in assessments based on the day of “in-residence”&gt;</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Understands study procedures and voluntarily provides written informed consent. 
 Willing and able to abide by the study restrictions, including the lifestyle considerations in Section 5.3. 
@@ -10403,28 +10417,10 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>&lt;First Check-out/Day X&gt;</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>KeyValue</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>6 weeks</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>&lt;first Check-out/Day X&gt;</t>
+          <t>&lt;First Check-out/Day X&gt;</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -10442,16 +10438,34 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>&lt;Bullet list of lay terminology of all assessments required during first Check-out&gt;</t>
+          <t>&lt;first Check-out/Day X&gt;</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>KeyValue</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>6 weeks</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Bullet list of lay terminology of all assessments required during first Check-out&gt;</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Participants will abstain from ingesting caffeine- or xanthine-containing products (eg, coffee, tea, cola drinks, and chocolate) from 24 hours before Check-in until Check-out from the CRU. 
 Participants will abstain from alcohol from 48 hours before Check-in until Check-out from the CRU. 
@@ -10459,47 +10473,47 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>&lt;Bullet list of lay terminology of all assessments required during the non-residential period; note differences in assessments based on the days of “non-residential”&gt;</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr"/>
-      <c r="C29" s="2" t="inlineStr"/>
-      <c r="D29" s="2" t="inlineStr"/>
-    </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>&lt;Final Check-out/Day X&gt;</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Paragraph</t>
-        </is>
-      </c>
+          <t>&lt;Bullet list of lay terminology of all assessments required during the non-residential period; note differences in assessments based on the days of “non-residential”&gt;</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Donation of blood is not permitted from 8 weeks (16 weeks for double red cell donation) prior to Screening until 90 days after the final Follow-up visit.</t>
-        </is>
-      </c>
+      <c r="D30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>&lt;Bullet list of lay terminology of all assessments required during the follow-up period; note differences in assessments based on the day and cohort of “follow-up period”&gt;</t>
+          <t>&lt;Final Check-out/Day X&gt;</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Paragraph</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr"/>
       <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Donation of blood is not permitted from 8 weeks (16 weeks for double red cell donation) prior to Screening until 90 days after the final Follow-up visit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>&lt;Bullet list of lay terminology of all assessments required during the follow-up period; note differences in assessments based on the day and cohort of “follow-up period”&gt;</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>The Investigator is obligated to perform or arrange for the conduct of supplemental measurements and/or evaluations as medically indicated or as requested by the Sponsor (or designee) to elucidate the nature and/or causality of the AE or SAE as fully as possible. This may include additional laboratory tests or investigations, histopathological examinations, or consultation with other health care professionals. 
 If a participant dies during participation in the study or during a recognized Follow-up period, the Investigator will provide the Sponsor (or designee) with a copy of any post-mortem findings including histopathology. 
@@ -10508,38 +10522,28 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>&lt;lay terminology for repeat-dose portion of study&gt;</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Paragraph</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>The SAD portion of this study is a standard design for first-in-human testing with a monoclonal antibody. In addition, a 4-week repeated dose cohort will allow confirmation of the safety, tolerability, and repeat-dose PK and immunogenicity in the target population prior to proceeding to subsequent repeat-dose studies in a patient population.</t>
-        </is>
-      </c>
-    </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>&lt;state health authority&gt;</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr"/>
+          <t>&lt;lay terminology for repeat-dose portion of study&gt;</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Paragraph</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="inlineStr"/>
-      <c r="D33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>The SAD portion of this study is a standard design for first-in-human testing with a monoclonal antibody. In addition, a 4-week repeated dose cohort will allow confirmation of the safety, tolerability, and repeat-dose PK and immunogenicity in the target population prior to proceeding to subsequent repeat-dose studies in a patient population.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>&lt;CRO Name&gt;</t>
+          <t>&lt;state health authority&gt;</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr"/>
@@ -10549,53 +10553,45 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>&lt;XX years&gt;</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>KeyValue</t>
-        </is>
-      </c>
+          <t>&lt;CRO Name&gt;</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr"/>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>2 years</t>
-        </is>
-      </c>
+      <c r="D35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>&lt;Firstname Lastname&gt;</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr"/>
+          <t>&lt;XX years&gt;</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>KeyValue</t>
+        </is>
+      </c>
       <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>&lt;study drug ID&gt;</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>KeyValue</t>
-        </is>
-      </c>
+          <t>&lt;Firstname Lastname&gt;</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr"/>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>ABC-123</t>
-        </is>
-      </c>
+      <c r="D37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>&lt;XX years&gt;</t>
+          <t>&lt;study drug ID&gt;</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -10606,42 +10602,42 @@
       <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>2 years</t>
+          <t>ABC-123</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>&lt;Firstname Lastname&gt;</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr"/>
+          <t>&lt;XX years&gt;</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>KeyValue</t>
+        </is>
+      </c>
       <c r="C39" s="2" t="inlineStr"/>
-      <c r="D39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>&lt;Study drug ID&gt;</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>KeyValue</t>
-        </is>
-      </c>
+          <t>&lt;Firstname Lastname&gt;</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>ABC-123</t>
-        </is>
-      </c>
+      <c r="D40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>&lt;study drug ID&gt;</t>
+          <t>&lt;Study drug ID&gt;</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -10677,33 +10673,25 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>&lt;Bullet list of lay terminology summarizing the protocol listed acceptable second methods of contraception.&gt;</t>
+          <t>&lt;study drug ID&gt;</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>KeyValue</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Understands study procedures and voluntarily provides written informed consent. 
-Willing and able to abide by the study restrictions, including the lifestyle considerations in Section 5.3. 
-Willing and able to complete all study visits, in-residence requirements, and procedures. 
-18 to 65 years of age at the time of signing informed consent. 
-Body mass index (BMI) between 18.0 and 35.0 kg/m2, inclusive, at Screening. 
-Female participants will be of non-childbearing potential (refer to Section 10.5 [Appendix 5] for definition of non-childbearing potential). 
-Male participants will agree to use contraception while on study intervention and for at least 6 months after the last dose of study intervention. 
-SAD cohorts only: Participants must be in good health, determined by no clinically significant findings from medical history, physical examination, 12-lead ECG, vital signs measurements, and clinical laboratory evaluations (see exclusion criteria for criteria for specific labs) at Screening as assessed by the Investigator. Clinical laboratory assessments may be repeated once at the Investigator’s discretion if laboratory error is suspected. 
-Repeat-dose cohort only: boneitis treated with Zammoxin or myrnestristoate and in otherwise good health except for well-controlled common conditions associated with boneitis, such as acid sweat or tonsillar invisibility. Clinical laboratory assessments may be repeated once at the Investigator’s discretion if laboratory error is suspected.</t>
+          <t>ABC-123</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>&lt;Lay terminology summarizing pregnancy information collection practices for male participants with partners who become pregnant.&gt;</t>
+          <t>&lt;Bullet list of lay terminology summarizing the protocol criteria for women to be not considered a WOCBP&gt;</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -10713,13 +10701,23 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;If a male participant's partner becomes pregnant during the study, the study team will ask for the partner's permission to collect information about her pregnancy. This information helps monitor the health of both the mother and baby. The study team will follow up with the partner, with her consent, to learn about the outcome of the pregnancy, and will share this information with the study sponsor. Any end of pregnancy, such as miscarriage or termination, will also be reported, regardless of the reason.&lt;/p&gt;</t>
+          <t>&lt;li&gt;You have not started having periods (premenarchal).&lt;/li&gt;&lt;li&gt;You have had your uterus removed (hysterectomy).&lt;/li&gt;&lt;li&gt;You have had both fallopian tubes removed (bilateral salpingectomy).&lt;/li&gt;&lt;li&gt;You have had both ovaries removed (bilateral oophorectomy).&lt;/li&gt;&lt;li&gt;You are permanently infertile due to another medical reason (such as certain medical conditions), as determined by your doctor.&lt;/li&gt;&lt;li&gt;You have not had a period for 12 months in a row and there is no other medical reason for this (postmenopausal).&lt;/li&gt;</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>The Investigator will attempt to collect pregnancy information on any male participant’s female partner who becomes pregnant while the male participant is in this study. This applies only to male participants who receive study intervention. 
-After obtaining the necessary signed informed consent from the pregnant female partner directly, the Investigator will record pregnancy information on the appropriate form and submit it to the Sponsor within 24 hours of learning of the partner’s pregnancy. The female partner will also be followed to determine the outcome of the pregnancy. Information on the status of the mother and child will be forwarded to the Sponsor. Generally, the follow-up will be no longer than 6 to 8 weeks following the estimated delivery date. Any termination of the pregnancy will be reported regardless of fetal status (presence or absence of anomalies) or indication for the procedure.</t>
+          <t>Women in the following categories are not considered WOCBP 
+Premenarchal 
+Premenopausal female with 1 of the following: 
+Documented hysterectomy 
+Documented bilateral salpingectomy 
+Documented bilateral oophorectomy 
+For individuals with permanent infertility due to an alternate medical cause other than the above, (eg, mullerian agenesis, androgen insensitivity), cause should be documented, and Investigator discretion should be applied to determining study entry. 
+Note: Documentation can come from the site personnel’s: review of the participant’s medical records, medical examination, or medical history interview. 
+Postmenopausal female 
+A postmenopausal state is defined as no menses for 12 months without an alternative medical cause. 
+A high follicle-stimulating hormone (FSH) level in the postmenopausal range may be used to confirm a postmenopausal state in women not using hormonal contraception or hormone replacement therapy (HRT). However, in the absence of 12 months of amenorrhea, confirmation with more than one FSH measurement consistent with postmenopausal status is required. 
+Females on HRT and whose menopausal status is in doubt will be required to use one of the non-estrogen hormonal highly effective contraception methods if they wish to continue their HRT during the study. Otherwise, they must discontinue HRT to allow confirmation of postmenopausal status before study enrollment.</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10786,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>(Study Doctor)Medical Investigator</t>
+          <t>Medical Investigator</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -10810,7 +10808,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Medical Investigator                     Stendarr, Inc. IRB Approved Version DD Mon YYYY</t>
+          <t>Medical Investigator</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -10832,7 +10830,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Medical Investigator                     Stendarr, Inc. IRB Approved Version DD Mon YYYY</t>
+          <t>Medical Investigator</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -10854,7 +10852,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Compensation (amount)</t>
+          <t>Medical Investigator</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -10876,7 +10874,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Follow-Up Period</t>
+          <t>Medical Investigator</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -10920,7 +10918,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>The study design includes a single ascending dose (SAD) component, which is double-blind, randomized, and placebo-controlled, involving up to six cohorts of healthy participants.</t>
+          <t>ABC-123</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -10942,7 +10940,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>No serious adverse effects were observed in blorp knockout mice, supporting the general safety of blorp inductors.</t>
+          <t>ABC-123</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -10964,7 +10962,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>HOW LONG THE STUDY WILL LAST AND WHO WILL BE IN THE STUDY</t>
+          <t>ABC-123</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -10986,7 +10984,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Study Procedures Check-in/Day 1</t>
+          <t>ABC-123</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -11008,7 +11006,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>The sponsor would like to keep the blood samples collected in the course of the study for future research to continue analyzing it for genes involved in the safety, pharmacokinetics (what the body does to a drug) and pharmacodynamics (how a medicine acts in the body) of the study drug, ABC-123. This information may be useful in increasing the knowledge of differences among individuals in the way they metabolize the investigational product as well as helping in the development of new drugs or improvement of existing drugs. You will not have any right to any such products or inventions or be entitled to any financial benefits from any such products. The information may be published or used for regulatory filings, but your identity will never be disclosed.</t>
+          <t>ABC-123</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -11030,7 +11028,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ABC-123 has not been given to humans, so no information about side effects are available.</t>
+          <t>ABC-123</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -11052,7 +11050,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Non-Physical Risks Associated with the Planned Genetic Analysis and Future Research of Biomarker Samples:</t>
+          <t>ABC-123</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -11074,7 +11072,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Be aware that this Federal law does not protect you against genetic discrimination by companies that sell life insurance, disability insurance, or long term-care insurance, nor does it prohibit discrimination based on a genetic disease or disorder that you already know about.</t>
+          <t>ABC-123</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -11096,7 +11094,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Risks of Subcutaneous (SC) Injection:</t>
+          <t>ABC-123</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -11118,7 +11116,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>If you participate in the repeat-dose portion of the study, the study should take about 1 week of your time and you will be given a subcutaneous injection of ABC-123 or placebo every other week for 3 doses.</t>
+          <t>the repeat-dose portion of the study</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -11140,7 +11138,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>You cannot be in this study if you meet any of the following criteria:</t>
+          <t>the repeat-dose portion of the study</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -11162,7 +11160,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Screening</t>
+          <t>the repeat-dose portion of the study</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -11184,7 +11182,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>KEY INFORMATION</t>
+          <t>the repeat-dose portion of the study</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -11206,7 +11204,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>the single ascending dose (SAD) portion of the study, involving cohorts of healthy participants:</t>
+          <t>the repeat-dose portion of the study</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -11228,7 +11226,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>You must be of non-childbearing potential (not able to have children) to be in this study. This includes:</t>
+          <t>the repeat-dose portion of the study</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -11250,7 +11248,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>If you are enrolled in the repeat-dose portion of the study you may benefit from ABC-123 for your boneitis.</t>
+          <t>the repeat-dose portion of the study</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -11272,7 +11270,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>IF YOU ANSWERED “NO” TO ANY OF THE ABOVE QUESTIONS, OR YOU ARE UNABLE TO ANSWER ANY OF THE ABOVE QUESTIONS,</t>
+          <t>the repeat-dose portion of the study</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -11294,7 +11292,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>If you are injured from your participation in this study, you should contact the study doctor as soon as possible in person or at the telephone number listed on page one of this consent form. Medical care may be obtained in the same way you would ordinarily obtain other medical treatment. If you suffer a physical injury that is directly caused by the study drug given as described in the study protocol or by a properly performed medical procedure required by the protocol, the reasonable costs of necessary medical treatment of the injury will be reimbursed by the Sponsor to the extent these costs are not covered by your insurance or other third-party coverage.</t>
+          <t>the repeat-dose portion of the study</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -11316,7 +11314,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Participant Responsibilities:</t>
+          <t>5 mg</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -11338,7 +11336,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>single ascending dose phase:</t>
+          <t>318-fold</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -11360,7 +11358,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Tell the study doctor or the study staff if you change your mind about staying in the study.</t>
+          <t>Cohorts 1–6</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -11382,7 +11380,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Alcohol consumption is prohibited from 48 hours before Check-in until Check-out from the CRU.</t>
+          <t>Cohorts 1–6</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -11394,7 +11392,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>&lt;Bullet list of lay terminology of all assessments required during the follow-up period; note differences in assessments based on the day and cohort of “follow-up period”&gt;</t>
+          <t>&lt;Bulleted list of lay terminology summarizing lifestyle considerations including meal requirements, caffeeine, alcohol, tobacco, and activity&gt;</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -11402,14 +11400,10 @@
           <t>LIST</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Routine physical examinations and vital sign monitoring, including blood pressure, pulse rate, respiratory rate, and body temperature.12-lead ECG to assess heart function.Clinical laboratory tests, such as blood chemistry, hematology, lipid profile, and cytokine assessments.Mental health evaluations to monitor psychological well-being.Adverse event tracking and recording concomitant medication use.Specific assessments tailored to the day of in-residence, with additional focus on pharmacokinetic and pharmacodynamic sampling as required..</t>
-        </is>
-      </c>
+      <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>UNRESOLVED</t>
         </is>
       </c>
     </row>
@@ -11426,7 +11420,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>The crunge.</t>
+          <t>Blood sampling for exploratory PD and safety biomarkers, including up to 3 additional samples per treatment period.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -11438,7 +11432,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>&lt;Bullet list of lay terminology of all assessments required during the first in-residence period; note differences in assessments based on the day of “in-residence”&gt;</t>
+          <t>&lt;Bullet list of lay terminology of all assessments required during the follow-up period; note differences in assessments based on the day and cohort of “follow-up period”&gt;</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -11448,7 +11442,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Blood sampling for exploratory PD and safety biomarkers, including up to 3 additional samples per treatment period.Monitoring of liver enzyme levels (ALT, AST) and other hepatic indicators as per the Schedule of Assessments.Physical examinations and detailed history taking for participants with elevated liver enzymes (&gt;3 × ULN).Laboratory tests including ALT, AST, bilirubin levels, alkaline phosphatase, and gamma glutamyltransferase.Liver ultrasound and tests for acetaminophen toxicity and viral hepatitis causes if indicated..</t>
+          <t>Blood sampling for exploratory PD and safety biomarkers, including up to 3 additional samples per treatment period.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -11460,17 +11454,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>&lt;First Check-out/Day X&gt;</t>
+          <t>&lt;Bullet list of lay terminology of all assessments required during the first in-residence period; note differences in assessments based on the day of “in-residence”&gt;</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>PARAGRAPH</t>
+          <t>LIST</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>The following will be done if you leave the study early:</t>
+          <t>Routine physical examinations and vital sign monitoring, including blood pressure, pulse rate, respiratory rate, and body temperature.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -11482,17 +11476,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>&lt;first Check-out/Day X&gt;</t>
+          <t>&lt;First Check-out/Day X&gt;</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>KEYVALUE</t>
+          <t>PARAGRAPH</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Blood samples will be taken by single needle-sticks or by a tube that is left in your arm. You cannot choose how the blood is taken.</t>
+          <t>Following Check-out from the CRU, all participants will return for Follow-up study visits up to 6 weeks post dosing in the first 3 cohorts and 10 weeks post dosing in the remaining cohorts, as detailed in the Schedule of Assessments.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -11504,17 +11498,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>&lt;Bullet list of lay terminology of all assessments required during first Check-out&gt;</t>
+          <t>&lt;first Check-out/Day X&gt;</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>LIST</t>
+          <t>KEYVALUE</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Vital sign monitoring: Includes measurements of blood pressure, pulse rate, respiratory rate, and body temperature.12-lead ECG: Used to assess heart function.Clinical laboratory tests: Evaluations of chemistry, hematology, lipid profile, and cytokine levels.Physical examinations: Comprehensive health check-ups.Mental health assessments: Evaluations to ensure psychological well-being.Adverse events monitoring: Observations to identify any negative health impacts.Concomitant medication tracking: Documentation of other medications taken during the study..</t>
+          <t>Following Check-out from the CRU, all participants will return for Follow-up study visits up to 6 weeks post dosing in the first 3 cohorts and 10 weeks post dosing in the remaining cohorts, as detailed in the Schedule of Assessments.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -11526,7 +11520,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>&lt;Bullet list of lay terminology of all assessments required during the non-residential period; note differences in assessments based on the days of “non-residential”&gt;</t>
+          <t>&lt;Bullet list of lay terminology of all assessments required during first Check-out&gt;</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -11536,7 +11530,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Physical risks: you may have a sore arm from where the blood sample is taken.</t>
+          <t>12-lead ECG</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -11548,17 +11542,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>&lt;state health authority&gt;</t>
+          <t>&lt;Bullet list of lay terminology of all assessments required during the non-residential period; note differences in assessments based on the days of “non-residential”&gt;</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>KEYVALUE</t>
+          <t>LIST</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Blood Samples (taken by single needle-sticks or by a tube that is left in your arm):</t>
+          <t>Safety measurements, such as ECG, vital signs, laboratory tests, and physical examinations, will be conducted at specific intervals according to the Schedule of Activities (SoA)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -11570,7 +11564,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>&lt;XX years&gt;</t>
+          <t>&lt;state health authority&gt;</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -11580,7 +11574,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Your DNA sample will be labeled with a code and not with your name or birthday to protect your identity and will be stored in a secure location until it is all used up or 30 years, whichever is sooner. You can ask for your DNA sample to be destroyed at any time and your sample will not be used for any new research, but any research data that has already been generated will not be destroyed.</t>
+          <t>local regulatory authority</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -11602,7 +11596,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>The sample will be retained in a secure location until the deoxyribonucleic acid (DNA - the material that determines your unique characteristics such as eye and hair color, and also influences the way your body responds to certain drugs and hereditary disease factors) has been exhausted, until the sponsor instructs the genotyping contractor to destroy the sample in accordance with laboratory procedures, or for 2 years. During this time, the DNA sample will not be immortalized or sold to anyone.</t>
+          <t>30 years</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -11614,7 +11608,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>&lt;Firstname Lastname&gt;</t>
+          <t>&lt;XX years&gt;</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -11624,7 +11618,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Address Line 1</t>
+          <t>30 years</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -11646,7 +11640,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Address Line 1</t>
+          <t>&lt;Firstname Lastname&gt;</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -11658,17 +11652,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>&lt;Bullet list of lay terminology summarizing the protocol listed acceptable second methods of contraception.&gt;</t>
+          <t>&lt;Firstname Lastname&gt;</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>LIST</t>
+          <t>KEYVALUE</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>If it becomes harmful to your health</t>
+          <t>&lt;Firstname Lastname&gt;</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11680,22 +11674,18 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>&lt;Lay terminology summarizing pregnancy information collection practices for male participants with partners who become pregnant.&gt;</t>
+          <t>&lt;Bullet list of lay terminology summarizing the protocol criteria for women to be not considered a WOCBP&gt;</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>PARAGRAPH</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>NEW FINDINGS</t>
-        </is>
-      </c>
+          <t>LIST</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>UNRESOLVED</t>
         </is>
       </c>
     </row>
@@ -11712,7 +11702,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Warmth or drainage</t>
+          <t>contact@trialstudy.com</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11732,7 +11722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -11890,104 +11880,146 @@
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Exact MATCH</t>
+          <t>Exact MATCH (&gt;=95% sim)</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Partial (&gt;=80%)</t>
+          <t>High Partial (&gt;=70% sim)</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>MISMATCH</t>
+          <t>Low Similarity (&gt;=50% sim)</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>78</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>QA has content, Pipeline empty</t>
+          <t>MISMATCH</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Exact match rate</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>7.14%</t>
-        </is>
+          <t>QA empty / Pipeline has content</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr"/>
-      <c r="B24" s="8" t="inlineStr"/>
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Pipeline empty</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>SUMMARY</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr"/>
+          <t>Both empty</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Out of 128 QA entries:</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr"/>
+          <t>Exact match rate</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>30.12%</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - 84 found in pipeline output</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr"/>
+          <t>Acceptable (&gt;=70% sim)</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>48.19%</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 44 MISSING from pipeline output</t>
-        </is>
-      </c>
+      <c r="A28" s="8" t="inlineStr"/>
       <c r="B28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
+          <t>SUMMARY</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Out of 128 QA entries:</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 84 found in pipeline output</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 44 MISSING from pipeline output</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">  - 43 extra in pipeline not in QA</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr"/>
+      <c r="B33" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
